--- a/tests/fixtures/squad-template/Unicode-names.xlsx
+++ b/tests/fixtures/squad-template/Unicode-names.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,11 +508,6 @@
           <t>Player Name *</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Default No.</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -530,9 +525,6 @@
   O’Neill</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,143 +549,108 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="1" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="1" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="1" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="1" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="1" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="1" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="1" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="1" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="1" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="1" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="1" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="1" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="1" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="1" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
